--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192B466F-224E-4A9C-875F-EB01C23AC5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155097B6-2F0A-47D6-A685-D7CAFE0A1767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -768,14 +768,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -786,7 +786,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -802,13 +802,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -819,7 +819,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>81</v>
       </c>
@@ -830,7 +830,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -846,17 +846,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -869,22 +869,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -898,28 +898,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.21875" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>39</v>
@@ -1103,10 +1103,10 @@
         <v>53</v>
       </c>
       <c r="AE2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>38</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>39</v>
@@ -2148,7 +2148,7 @@
         <v>53</v>
       </c>
       <c r="AE13">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2161,37 +2161,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>73</v>
       </c>
@@ -2204,19 +2204,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -2276,15 +2276,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
@@ -2298,21 +2298,24 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>103</v>
+      <c r="B2" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>43</v>
       </c>
+      <c r="D2" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="E2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>100</v>
       </c>
@@ -2329,7 +2332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>100</v>
       </c>
@@ -2346,7 +2349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>100</v>
       </c>
@@ -2363,7 +2366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>100</v>
       </c>
@@ -2380,7 +2383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>100</v>
       </c>
@@ -2397,7 +2400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>100</v>
       </c>
@@ -2414,7 +2417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>100</v>
       </c>
@@ -2431,7 +2434,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>100</v>
       </c>
@@ -2448,7 +2451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>100</v>
       </c>
@@ -2465,7 +2468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>100</v>
       </c>
@@ -2482,21 +2485,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>102</v>
+      <c r="B13" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="E13">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2507,7 +2507,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF4DCB0-85D6-4076-87FF-4126675E54C9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155097B6-2F0A-47D6-A685-D7CAFE0A1767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F862FCE5-E0FD-4A57-B2BE-A9DED08F841F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,9 @@
     <sheet name="InternalTeams" sheetId="18" r:id="rId6"/>
     <sheet name="AddContact" sheetId="14" r:id="rId7"/>
     <sheet name="Engagement" sheetId="20" r:id="rId8"/>
-    <sheet name="Sheet2" sheetId="21" r:id="rId9"/>
+    <sheet name="OppDealTeamMembers" sheetId="21" r:id="rId9"/>
+    <sheet name="Roles" sheetId="22" r:id="rId10"/>
+    <sheet name="OverlimitMessage" sheetId="23" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="164">
   <si>
     <t>James Craven</t>
   </si>
@@ -356,6 +358,186 @@
   </si>
   <si>
     <t>TAS - Due Diligence Services</t>
+  </si>
+  <si>
+    <t>OppDealTeamMembers</t>
+  </si>
+  <si>
+    <t>Elaine Pan</t>
+  </si>
+  <si>
+    <t>Aaron Schultz</t>
+  </si>
+  <si>
+    <t>Ben Chiu</t>
+  </si>
+  <si>
+    <t>Blair Richardson</t>
+  </si>
+  <si>
+    <t>Conrad Kolasa</t>
+  </si>
+  <si>
+    <t>Dimitri Drone</t>
+  </si>
+  <si>
+    <t>Jason Vierig</t>
+  </si>
+  <si>
+    <t>Karim Jooma</t>
+  </si>
+  <si>
+    <t>Kyle Poorman</t>
+  </si>
+  <si>
+    <t>Marshall Taylor</t>
+  </si>
+  <si>
+    <t>Matt Kavney</t>
+  </si>
+  <si>
+    <t>Matt Sturgell</t>
+  </si>
+  <si>
+    <t>Michael Chiu</t>
+  </si>
+  <si>
+    <t>Ozzie Ozdemir</t>
+  </si>
+  <si>
+    <t>Paul Birchwood</t>
+  </si>
+  <si>
+    <t>Prashant Kamath</t>
+  </si>
+  <si>
+    <t>Preston Wolf</t>
+  </si>
+  <si>
+    <t>Ali Amin</t>
+  </si>
+  <si>
+    <t>Rittik Chakrabarti</t>
+  </si>
+  <si>
+    <t>Robert Zarnoch</t>
+  </si>
+  <si>
+    <t>Ryan Verola</t>
+  </si>
+  <si>
+    <t>Ryan Mahlan</t>
+  </si>
+  <si>
+    <t>Sid Chitnis</t>
+  </si>
+  <si>
+    <t>Susanna O'Brien</t>
+  </si>
+  <si>
+    <t>Zach Hamilton</t>
+  </si>
+  <si>
+    <t>Rebecca Hu</t>
+  </si>
+  <si>
+    <t>Timothy Kang</t>
+  </si>
+  <si>
+    <t>Abhinav Pal</t>
+  </si>
+  <si>
+    <t>Adam Dunayer</t>
+  </si>
+  <si>
+    <t>Adam Ishola</t>
+  </si>
+  <si>
+    <t>Adam Schor</t>
+  </si>
+  <si>
+    <t>Aditi Singh</t>
+  </si>
+  <si>
+    <t>Aditya Aiyer</t>
+  </si>
+  <si>
+    <t>Aditya Tyagi</t>
+  </si>
+  <si>
+    <t>Adnan Sura</t>
+  </si>
+  <si>
+    <t>Adriana Stacey</t>
+  </si>
+  <si>
+    <t>Afnan Ahmed</t>
+  </si>
+  <si>
+    <t>Ahmed Elbiltagui</t>
+  </si>
+  <si>
+    <t>Aidan Fitzgibbon</t>
+  </si>
+  <si>
+    <t>AJ Amankwaa</t>
+  </si>
+  <si>
+    <t>Ajay Arelli</t>
+  </si>
+  <si>
+    <t>Akshat Jamad</t>
+  </si>
+  <si>
+    <t>Alex Dochter</t>
+  </si>
+  <si>
+    <t>Alberico Altieri</t>
+  </si>
+  <si>
+    <t>Allen Plunk</t>
+  </si>
+  <si>
+    <t>Albert Sung</t>
+  </si>
+  <si>
+    <t>Alfonso Garcia</t>
+  </si>
+  <si>
+    <t>Aleksandra Chadam</t>
+  </si>
+  <si>
+    <t>Alessandro Ciravegna</t>
+  </si>
+  <si>
+    <t>Alessandro Rossi</t>
+  </si>
+  <si>
+    <t>Alexander Garcia</t>
+  </si>
+  <si>
+    <t>Alex Cohen</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>Associate</t>
+  </si>
+  <si>
+    <t>OverlimitMessage</t>
+  </si>
+  <si>
+    <t>MaxMembersLimit</t>
+  </si>
+  <si>
+    <t>Please remove and re-add the following deal team member(s) to the internal team and then add the desired role(s). Removing the deal team member will allow the Office Allocation field to re-populate.</t>
+  </si>
+  <si>
+    <t>52</t>
   </si>
 </sst>
 </file>
@@ -471,7 +653,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -486,6 +668,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,6 +987,76 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FB3C8-D05A-4A1D-9559-104A9F0AD28A}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="56.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
@@ -1011,7 +1269,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -1106,44 +1364,44 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:31" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="F3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="I3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="4" t="s">
         <v>44</v>
       </c>
       <c r="N3" t="s">
@@ -1158,10 +1416,10 @@
       <c r="Q3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="4" t="s">
         <v>46</v>
       </c>
       <c r="T3" s="3" t="s">
@@ -1170,19 +1428,19 @@
       <c r="U3" t="s">
         <v>48</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="X3" t="s">
+      <c r="X3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Y3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="Z3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AA3" s="3" t="s">
@@ -1198,7 +1456,7 @@
         <v>53</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
@@ -1208,8 +1466,8 @@
       <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>84</v>
+      <c r="C4" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="D4" t="s">
         <v>39</v>
@@ -1290,10 +1548,10 @@
         <v>83</v>
       </c>
       <c r="AD4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AE4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
@@ -1304,7 +1562,7 @@
         <v>38</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
         <v>39</v>
@@ -1385,10 +1643,10 @@
         <v>83</v>
       </c>
       <c r="AD5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="AE5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
@@ -1399,7 +1657,7 @@
         <v>38</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
         <v>39</v>
@@ -1480,10 +1738,10 @@
         <v>83</v>
       </c>
       <c r="AD6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AE6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
@@ -1494,7 +1752,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
@@ -1575,10 +1833,10 @@
         <v>83</v>
       </c>
       <c r="AD7" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="AE7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
@@ -1589,7 +1847,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
         <v>39</v>
@@ -1670,10 +1928,10 @@
         <v>83</v>
       </c>
       <c r="AD8" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AE8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
@@ -1684,7 +1942,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
@@ -1765,10 +2023,10 @@
         <v>83</v>
       </c>
       <c r="AD9" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="AE9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
@@ -1779,7 +2037,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1860,21 +2118,21 @@
         <v>83</v>
       </c>
       <c r="AD10" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AE10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>91</v>
+      <c r="C11" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
@@ -1955,21 +2213,21 @@
         <v>83</v>
       </c>
       <c r="AD11" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="AE11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>38</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>92</v>
+      <c r="C12" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
@@ -2053,47 +2311,47 @@
         <v>53</v>
       </c>
       <c r="AE12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="C13" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="I13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" t="s">
         <v>78</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" t="s">
         <v>43</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" t="s">
         <v>44</v>
       </c>
       <c r="N13" t="s">
@@ -2108,10 +2366,10 @@
       <c r="Q13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="R13" s="4" t="s">
+      <c r="R13" t="s">
         <v>46</v>
       </c>
-      <c r="S13" s="4" t="s">
+      <c r="S13" t="s">
         <v>46</v>
       </c>
       <c r="T13" s="3" t="s">
@@ -2120,19 +2378,19 @@
       <c r="U13" t="s">
         <v>48</v>
       </c>
-      <c r="V13" s="4" t="s">
+      <c r="V13" t="s">
         <v>49</v>
       </c>
-      <c r="W13" s="4" t="s">
+      <c r="W13" t="s">
         <v>50</v>
       </c>
-      <c r="X13" s="4" t="s">
+      <c r="X13" t="s">
         <v>51</v>
       </c>
-      <c r="Y13" s="4" t="s">
+      <c r="Y13" t="s">
         <v>79</v>
       </c>
-      <c r="Z13" s="4" t="s">
+      <c r="Z13" t="s">
         <v>52</v>
       </c>
       <c r="AA13" s="3" t="s">
@@ -2148,7 +2406,7 @@
         <v>53</v>
       </c>
       <c r="AE13">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2298,7 +2556,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>100</v>
       </c>
@@ -2315,21 +2573,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+    <row r="3" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="E3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2342,11 +2597,11 @@
       <c r="C4" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>84</v>
+      <c r="D4" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2360,10 +2615,10 @@
         <v>43</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2377,10 +2632,10 @@
         <v>43</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2394,10 +2649,10 @@
         <v>43</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2411,10 +2666,10 @@
         <v>43</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2428,10 +2683,10 @@
         <v>43</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2445,13 +2700,13 @@
         <v>43</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>100</v>
       </c>
@@ -2461,14 +2716,14 @@
       <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>91</v>
+      <c r="D11" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="E11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>100</v>
       </c>
@@ -2478,25 +2733,28 @@
       <c r="C12" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E12">
+      <c r="E13">
         <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2506,9 +2764,278 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF4DCB0-85D6-4076-87FF-4126675E54C9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F862FCE5-E0FD-4A57-B2BE-A9DED08F841F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EAC2AC-9332-411B-BC7D-4A5F94260813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -569,6 +569,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1177,7 +1178,7 @@
     <col min="31" max="31" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1269,44 +1270,44 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="4" t="s">
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="4" t="s">
+      <c r="I2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
         <v>78</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" t="s">
         <v>43</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" t="s">
         <v>44</v>
       </c>
       <c r="N2" t="s">
@@ -1321,10 +1322,10 @@
       <c r="Q2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" t="s">
         <v>46</v>
       </c>
       <c r="T2" s="3" t="s">
@@ -1333,19 +1334,19 @@
       <c r="U2" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" t="s">
         <v>49</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" t="s">
         <v>50</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" t="s">
         <v>51</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" t="s">
         <v>79</v>
       </c>
-      <c r="Z2" s="4" t="s">
+      <c r="Z2" t="s">
         <v>52</v>
       </c>
       <c r="AA2" s="3" t="s">
@@ -1361,47 +1362,47 @@
         <v>53</v>
       </c>
       <c r="AE2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="F3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
         <v>78</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" t="s">
         <v>44</v>
       </c>
       <c r="N3" t="s">
@@ -1416,10 +1417,10 @@
       <c r="Q3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" t="s">
         <v>46</v>
       </c>
       <c r="T3" s="3" t="s">
@@ -1428,19 +1429,19 @@
       <c r="U3" t="s">
         <v>48</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" t="s">
         <v>49</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" t="s">
         <v>50</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" t="s">
         <v>51</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" t="s">
         <v>79</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3" t="s">
         <v>52</v>
       </c>
       <c r="AA3" s="3" t="s">
@@ -1453,10 +1454,10 @@
         <v>83</v>
       </c>
       <c r="AD3" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="AE3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
@@ -1466,8 +1467,8 @@
       <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>76</v>
+      <c r="C4" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="D4" t="s">
         <v>39</v>
@@ -1551,7 +1552,7 @@
         <v>53</v>
       </c>
       <c r="AE4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
@@ -1562,7 +1563,7 @@
         <v>38</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
         <v>39</v>
@@ -1646,7 +1647,7 @@
         <v>41</v>
       </c>
       <c r="AE5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
@@ -1657,7 +1658,7 @@
         <v>38</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
         <v>39</v>
@@ -1741,7 +1742,7 @@
         <v>53</v>
       </c>
       <c r="AE6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
@@ -1752,7 +1753,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
         <v>39</v>
@@ -1836,7 +1837,7 @@
         <v>41</v>
       </c>
       <c r="AE7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
@@ -1847,7 +1848,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
         <v>39</v>
@@ -1931,7 +1932,7 @@
         <v>53</v>
       </c>
       <c r="AE8">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
@@ -1942,7 +1943,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
         <v>39</v>
@@ -2026,18 +2027,18 @@
         <v>41</v>
       </c>
       <c r="AE9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>38</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>89</v>
+      <c r="C10" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -2121,7 +2122,7 @@
         <v>53</v>
       </c>
       <c r="AE10">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
@@ -2131,8 +2132,8 @@
       <c r="B11" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>90</v>
+      <c r="C11" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
@@ -2213,50 +2214,50 @@
         <v>83</v>
       </c>
       <c r="AD11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AE11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="F12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="I12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="N12" t="s">
@@ -2271,10 +2272,10 @@
       <c r="Q12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="R12" t="s">
+      <c r="R12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="S12" t="s">
+      <c r="S12" s="4" t="s">
         <v>46</v>
       </c>
       <c r="T12" s="3" t="s">
@@ -2283,19 +2284,19 @@
       <c r="U12" t="s">
         <v>48</v>
       </c>
-      <c r="V12" t="s">
+      <c r="V12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="W12" t="s">
+      <c r="W12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="X12" t="s">
+      <c r="X12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="Y12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="Z12" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AA12" s="3" t="s">
@@ -2311,47 +2312,47 @@
         <v>53</v>
       </c>
       <c r="AE12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="F13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="I13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="N13" t="s">
@@ -2366,10 +2367,10 @@
       <c r="Q13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="R13" t="s">
+      <c r="R13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="S13" t="s">
+      <c r="S13" s="4" t="s">
         <v>46</v>
       </c>
       <c r="T13" s="3" t="s">
@@ -2378,19 +2379,19 @@
       <c r="U13" t="s">
         <v>48</v>
       </c>
-      <c r="V13" t="s">
+      <c r="V13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="W13" t="s">
+      <c r="W13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="X13" t="s">
+      <c r="X13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Y13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="Z13" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AA13" s="3" t="s">
@@ -2406,7 +2407,7 @@
         <v>53</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EAC2AC-9332-411B-BC7D-4A5F94260813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789B0483-6441-4820-9215-423A1F0C39A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -2543,7 +2543,7 @@
     <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
@@ -2557,35 +2557,38 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>93</v>
+      <c r="D2" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="E2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>100</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
         <v>43</v>
       </c>
+      <c r="D3" s="6" t="s">
+        <v>84</v>
+      </c>
       <c r="E3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2598,11 +2601,11 @@
       <c r="C4" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>76</v>
+      <c r="D4" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2616,10 +2619,10 @@
         <v>43</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2633,10 +2636,10 @@
         <v>43</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2650,10 +2653,10 @@
         <v>43</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2667,10 +2670,10 @@
         <v>43</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2684,13 +2687,13 @@
         <v>43</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>100</v>
       </c>
@@ -2700,11 +2703,11 @@
       <c r="C10" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>89</v>
+      <c r="D10" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2717,45 +2720,42 @@
       <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>90</v>
+      <c r="D11" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="E11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>91</v>
+      <c r="D12" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="E12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>92</v>
-      </c>
       <c r="E13">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789B0483-6441-4820-9215-423A1F0C39A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE4D515-F067-41F6-A45E-4D490A8D6695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,9 +165,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -538,6 +535,9 @@
   </si>
   <si>
     <t>52</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -972,12 +972,12 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -999,20 +999,20 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -1031,26 +1031,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -1075,26 +1075,26 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1255,7 +1255,7 @@
         <v>34</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>35</v>
@@ -1264,7 +1264,7 @@
         <v>36</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>37</v>
@@ -1278,88 +1278,88 @@
         <v>38</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
       <c r="F2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" t="s">
         <v>42</v>
       </c>
-      <c r="I2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" t="s">
+        <v>45</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W2" t="s">
+        <v>49</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
         <v>78</v>
       </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" t="s">
-        <v>66</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" t="s">
-        <v>48</v>
-      </c>
-      <c r="V2" t="s">
-        <v>49</v>
-      </c>
-      <c r="W2" t="s">
-        <v>50</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>51</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AB2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD2" t="s">
         <v>52</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>53</v>
       </c>
       <c r="AE2">
         <v>1</v>
@@ -1373,88 +1373,88 @@
         <v>38</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
       <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" t="s">
         <v>42</v>
       </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" t="s">
+        <v>48</v>
+      </c>
+      <c r="W3" t="s">
+        <v>49</v>
+      </c>
+      <c r="X3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y3" t="s">
         <v>78</v>
       </c>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" t="s">
-        <v>66</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" t="s">
-        <v>48</v>
-      </c>
-      <c r="V3" t="s">
-        <v>49</v>
-      </c>
-      <c r="W3" t="s">
-        <v>50</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>51</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="AB3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE3">
         <v>2</v>
@@ -1468,88 +1468,88 @@
         <v>38</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
       <c r="F4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" t="s">
         <v>41</v>
       </c>
-      <c r="G4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" t="s">
         <v>42</v>
       </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" t="s">
+        <v>47</v>
+      </c>
+      <c r="V4" t="s">
+        <v>48</v>
+      </c>
+      <c r="W4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y4" t="s">
         <v>78</v>
       </c>
-      <c r="L4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" t="s">
-        <v>66</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S4" t="s">
-        <v>46</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" t="s">
-        <v>48</v>
-      </c>
-      <c r="V4" t="s">
-        <v>49</v>
-      </c>
-      <c r="W4" t="s">
-        <v>50</v>
-      </c>
-      <c r="X4" t="s">
+      <c r="Z4" t="s">
         <v>51</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AA4" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AB4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD4" t="s">
         <v>52</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>53</v>
       </c>
       <c r="AE4">
         <v>3</v>
@@ -1563,88 +1563,88 @@
         <v>38</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" t="s">
         <v>39</v>
       </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
       <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
         <v>41</v>
       </c>
-      <c r="G5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" t="s">
         <v>42</v>
       </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U5" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" t="s">
+        <v>49</v>
+      </c>
+      <c r="X5" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y5" t="s">
         <v>78</v>
       </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5" t="s">
-        <v>44</v>
-      </c>
-      <c r="N5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R5" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U5" t="s">
-        <v>48</v>
-      </c>
-      <c r="V5" t="s">
-        <v>49</v>
-      </c>
-      <c r="W5" t="s">
-        <v>50</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="Z5" t="s">
         <v>51</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AA5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="AB5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE5">
         <v>4</v>
@@ -1658,88 +1658,88 @@
         <v>38</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" t="s">
         <v>39</v>
       </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
       <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" t="s">
+        <v>77</v>
+      </c>
+      <c r="L6" t="s">
         <v>42</v>
       </c>
-      <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U6" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" t="s">
+        <v>48</v>
+      </c>
+      <c r="W6" t="s">
+        <v>49</v>
+      </c>
+      <c r="X6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y6" t="s">
         <v>78</v>
       </c>
-      <c r="L6" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" t="s">
-        <v>66</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R6" t="s">
-        <v>46</v>
-      </c>
-      <c r="S6" t="s">
-        <v>46</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U6" t="s">
-        <v>48</v>
-      </c>
-      <c r="V6" t="s">
-        <v>49</v>
-      </c>
-      <c r="W6" t="s">
-        <v>50</v>
-      </c>
-      <c r="X6" t="s">
+      <c r="Z6" t="s">
         <v>51</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AA6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AB6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s">
         <v>52</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>53</v>
       </c>
       <c r="AE6">
         <v>5</v>
@@ -1753,88 +1753,88 @@
         <v>38</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
       <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" t="s">
         <v>41</v>
       </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" t="s">
         <v>42</v>
       </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R7" t="s">
+        <v>45</v>
+      </c>
+      <c r="S7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V7" t="s">
+        <v>48</v>
+      </c>
+      <c r="W7" t="s">
+        <v>49</v>
+      </c>
+      <c r="X7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y7" t="s">
         <v>78</v>
       </c>
-      <c r="L7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N7" t="s">
-        <v>66</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R7" t="s">
-        <v>46</v>
-      </c>
-      <c r="S7" t="s">
-        <v>46</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U7" t="s">
-        <v>48</v>
-      </c>
-      <c r="V7" t="s">
-        <v>49</v>
-      </c>
-      <c r="W7" t="s">
-        <v>50</v>
-      </c>
-      <c r="X7" t="s">
+      <c r="Z7" t="s">
         <v>51</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="AA7" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="AB7" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE7">
         <v>6</v>
@@ -1848,88 +1848,88 @@
         <v>38</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
       <c r="F8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" t="s">
         <v>41</v>
       </c>
-      <c r="G8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" t="s">
         <v>42</v>
       </c>
-      <c r="I8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R8" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" t="s">
+        <v>45</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" t="s">
+        <v>48</v>
+      </c>
+      <c r="W8" t="s">
+        <v>49</v>
+      </c>
+      <c r="X8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y8" t="s">
         <v>78</v>
       </c>
-      <c r="L8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N8" t="s">
-        <v>66</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R8" t="s">
-        <v>46</v>
-      </c>
-      <c r="S8" t="s">
-        <v>46</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U8" t="s">
-        <v>48</v>
-      </c>
-      <c r="V8" t="s">
-        <v>49</v>
-      </c>
-      <c r="W8" t="s">
-        <v>50</v>
-      </c>
-      <c r="X8" t="s">
+      <c r="Z8" t="s">
         <v>51</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AA8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AB8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD8" t="s">
         <v>52</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>53</v>
       </c>
       <c r="AE8">
         <v>7</v>
@@ -1943,88 +1943,88 @@
         <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E9" t="s">
         <v>39</v>
       </c>
-      <c r="E9" t="s">
-        <v>40</v>
-      </c>
       <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
         <v>41</v>
       </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" t="s">
         <v>42</v>
       </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R9" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9" t="s">
+        <v>45</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V9" t="s">
+        <v>48</v>
+      </c>
+      <c r="W9" t="s">
+        <v>49</v>
+      </c>
+      <c r="X9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y9" t="s">
         <v>78</v>
       </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9" t="s">
-        <v>66</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R9" t="s">
-        <v>46</v>
-      </c>
-      <c r="S9" t="s">
-        <v>46</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U9" t="s">
-        <v>48</v>
-      </c>
-      <c r="V9" t="s">
-        <v>49</v>
-      </c>
-      <c r="W9" t="s">
-        <v>50</v>
-      </c>
-      <c r="X9" t="s">
+      <c r="Z9" t="s">
         <v>51</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="AA9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z9" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="AB9" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AC9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AE9">
         <v>8</v>
@@ -2038,88 +2038,88 @@
         <v>38</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E10" t="s">
         <v>39</v>
       </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
       <c r="F10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
         <v>41</v>
       </c>
-      <c r="G10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" t="s">
+        <v>77</v>
+      </c>
+      <c r="L10" t="s">
         <v>42</v>
       </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R10" t="s">
+        <v>45</v>
+      </c>
+      <c r="S10" t="s">
+        <v>45</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" t="s">
+        <v>47</v>
+      </c>
+      <c r="V10" t="s">
+        <v>48</v>
+      </c>
+      <c r="W10" t="s">
+        <v>49</v>
+      </c>
+      <c r="X10" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y10" t="s">
         <v>78</v>
       </c>
-      <c r="L10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10" t="s">
-        <v>66</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S10" t="s">
-        <v>46</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U10" t="s">
-        <v>48</v>
-      </c>
-      <c r="V10" t="s">
-        <v>49</v>
-      </c>
-      <c r="W10" t="s">
-        <v>50</v>
-      </c>
-      <c r="X10" t="s">
+      <c r="Z10" t="s">
         <v>51</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="AA10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="AB10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD10" t="s">
         <v>52</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>53</v>
       </c>
       <c r="AE10">
         <v>9</v>
@@ -2133,88 +2133,88 @@
         <v>38</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" t="s">
         <v>39</v>
       </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
       <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
         <v>41</v>
       </c>
-      <c r="G11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" t="s">
         <v>42</v>
       </c>
-      <c r="I11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" t="s">
+        <v>45</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" t="s">
+        <v>47</v>
+      </c>
+      <c r="V11" t="s">
+        <v>48</v>
+      </c>
+      <c r="W11" t="s">
+        <v>49</v>
+      </c>
+      <c r="X11" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y11" t="s">
         <v>78</v>
       </c>
-      <c r="L11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N11" t="s">
-        <v>66</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R11" t="s">
-        <v>46</v>
-      </c>
-      <c r="S11" t="s">
-        <v>46</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U11" t="s">
-        <v>48</v>
-      </c>
-      <c r="V11" t="s">
-        <v>49</v>
-      </c>
-      <c r="W11" t="s">
-        <v>50</v>
-      </c>
-      <c r="X11" t="s">
+      <c r="Z11" t="s">
         <v>51</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="AA11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AB11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD11" t="s">
         <v>52</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>53</v>
       </c>
       <c r="AE11">
         <v>10</v>
@@ -2228,88 +2228,88 @@
         <v>38</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="F12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="4" t="s">
+      <c r="M12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U12" t="s">
+        <v>47</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y12" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N12" t="s">
-        <v>66</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U12" t="s">
-        <v>48</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="X12" s="4" t="s">
+      <c r="Z12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Y12" s="4" t="s">
+      <c r="AA12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z12" s="4" t="s">
+      <c r="AB12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD12" t="s">
         <v>52</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>53</v>
       </c>
       <c r="AE12">
         <v>11</v>
@@ -2323,88 +2323,88 @@
         <v>38</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="F13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="M13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U13" t="s">
+        <v>47</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y13" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N13" t="s">
-        <v>66</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="U13" t="s">
-        <v>48</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="X13" s="4" t="s">
+      <c r="Z13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Y13" s="4" t="s">
+      <c r="AA13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="Z13" s="4" t="s">
+      <c r="AB13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD13" t="s">
         <v>52</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>53</v>
       </c>
       <c r="AE13">
         <v>12</v>
@@ -2427,7 +2427,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2437,22 +2437,22 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2477,54 +2477,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2545,30 +2545,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2576,16 +2576,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -2593,16 +2593,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2627,16 +2627,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -2644,16 +2644,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -2661,16 +2661,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -2678,16 +2678,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -2695,16 +2695,16 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -2712,16 +2712,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -2729,16 +2729,16 @@
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -2746,13 +2746,13 @@
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -2773,267 +2773,267 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE4D515-F067-41F6-A45E-4D490A8D6695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B80AA7-E63F-4277-90B1-5BE1C0EFE54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="163">
   <si>
     <t>James Craven</t>
   </si>
@@ -241,9 +241,6 @@
   </si>
   <si>
     <t>Kristian M. Whalen</t>
-  </si>
-  <si>
-    <t>William Peluchiwski</t>
   </si>
   <si>
     <t>Eric Cartier</t>
@@ -972,12 +969,12 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1002,17 +999,17 @@
         <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1031,26 +1028,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1060,7 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1075,26 +1072,26 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1142,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1166,7 +1163,7 @@
     <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -1255,7 +1252,7 @@
         <v>34</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>35</v>
@@ -1264,7 +1261,7 @@
         <v>36</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>37</v>
@@ -1278,10 +1275,10 @@
         <v>38</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>39</v>
@@ -1302,7 +1299,7 @@
         <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L2" t="s">
         <v>42</v>
@@ -1311,7 +1308,7 @@
         <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>44</v>
@@ -1344,19 +1341,19 @@
         <v>50</v>
       </c>
       <c r="Y2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z2" t="s">
         <v>51</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD2" t="s">
         <v>52</v>
@@ -1373,10 +1370,10 @@
         <v>38</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
         <v>39</v>
@@ -1397,7 +1394,7 @@
         <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L3" t="s">
         <v>42</v>
@@ -1406,7 +1403,7 @@
         <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>44</v>
@@ -1439,19 +1436,19 @@
         <v>50</v>
       </c>
       <c r="Y3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z3" t="s">
         <v>51</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD3" t="s">
         <v>40</v>
@@ -1468,10 +1465,10 @@
         <v>38</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>39</v>
@@ -1492,7 +1489,7 @@
         <v>40</v>
       </c>
       <c r="K4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L4" t="s">
         <v>42</v>
@@ -1501,7 +1498,7 @@
         <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>44</v>
@@ -1534,19 +1531,19 @@
         <v>50</v>
       </c>
       <c r="Y4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z4" t="s">
         <v>51</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD4" t="s">
         <v>52</v>
@@ -1563,10 +1560,10 @@
         <v>38</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
         <v>39</v>
@@ -1587,7 +1584,7 @@
         <v>40</v>
       </c>
       <c r="K5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L5" t="s">
         <v>42</v>
@@ -1596,7 +1593,7 @@
         <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>44</v>
@@ -1629,19 +1626,19 @@
         <v>50</v>
       </c>
       <c r="Y5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z5" t="s">
         <v>51</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD5" t="s">
         <v>40</v>
@@ -1658,10 +1655,10 @@
         <v>38</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E6" t="s">
         <v>39</v>
@@ -1682,7 +1679,7 @@
         <v>40</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s">
         <v>42</v>
@@ -1691,7 +1688,7 @@
         <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>44</v>
@@ -1724,19 +1721,19 @@
         <v>50</v>
       </c>
       <c r="Y6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z6" t="s">
         <v>51</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD6" t="s">
         <v>52</v>
@@ -1753,10 +1750,10 @@
         <v>38</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
         <v>39</v>
@@ -1777,7 +1774,7 @@
         <v>40</v>
       </c>
       <c r="K7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L7" t="s">
         <v>42</v>
@@ -1786,7 +1783,7 @@
         <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>44</v>
@@ -1819,19 +1816,19 @@
         <v>50</v>
       </c>
       <c r="Y7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z7" t="s">
         <v>51</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD7" t="s">
         <v>40</v>
@@ -1848,10 +1845,10 @@
         <v>38</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E8" t="s">
         <v>39</v>
@@ -1872,7 +1869,7 @@
         <v>40</v>
       </c>
       <c r="K8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L8" t="s">
         <v>42</v>
@@ -1881,7 +1878,7 @@
         <v>43</v>
       </c>
       <c r="N8" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>44</v>
@@ -1914,19 +1911,19 @@
         <v>50</v>
       </c>
       <c r="Y8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z8" t="s">
         <v>51</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD8" t="s">
         <v>52</v>
@@ -1943,10 +1940,10 @@
         <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E9" t="s">
         <v>39</v>
@@ -1967,7 +1964,7 @@
         <v>40</v>
       </c>
       <c r="K9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L9" t="s">
         <v>42</v>
@@ -1976,7 +1973,7 @@
         <v>43</v>
       </c>
       <c r="N9" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>44</v>
@@ -2009,19 +2006,19 @@
         <v>50</v>
       </c>
       <c r="Y9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z9" t="s">
         <v>51</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD9" t="s">
         <v>40</v>
@@ -2038,10 +2035,10 @@
         <v>38</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
         <v>39</v>
@@ -2062,7 +2059,7 @@
         <v>40</v>
       </c>
       <c r="K10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L10" t="s">
         <v>42</v>
@@ -2071,7 +2068,7 @@
         <v>43</v>
       </c>
       <c r="N10" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>44</v>
@@ -2104,19 +2101,19 @@
         <v>50</v>
       </c>
       <c r="Y10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z10" t="s">
         <v>51</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD10" t="s">
         <v>52</v>
@@ -2133,10 +2130,10 @@
         <v>38</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E11" t="s">
         <v>39</v>
@@ -2157,7 +2154,7 @@
         <v>40</v>
       </c>
       <c r="K11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L11" t="s">
         <v>42</v>
@@ -2166,7 +2163,7 @@
         <v>43</v>
       </c>
       <c r="N11" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>44</v>
@@ -2199,19 +2196,19 @@
         <v>50</v>
       </c>
       <c r="Y11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z11" t="s">
         <v>51</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD11" t="s">
         <v>52</v>
@@ -2228,10 +2225,10 @@
         <v>38</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>39</v>
@@ -2252,7 +2249,7 @@
         <v>40</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>42</v>
@@ -2261,7 +2258,7 @@
         <v>43</v>
       </c>
       <c r="N12" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>44</v>
@@ -2294,19 +2291,19 @@
         <v>50</v>
       </c>
       <c r="Y12" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z12" s="4" t="s">
         <v>51</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD12" t="s">
         <v>52</v>
@@ -2323,10 +2320,10 @@
         <v>38</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>39</v>
@@ -2347,7 +2344,7 @@
         <v>40</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L13" s="4" t="s">
         <v>42</v>
@@ -2356,7 +2353,7 @@
         <v>43</v>
       </c>
       <c r="N13" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>44</v>
@@ -2389,19 +2386,19 @@
         <v>50</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z13" s="4" t="s">
         <v>51</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AD13" t="s">
         <v>52</v>
@@ -2427,7 +2424,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2437,22 +2434,22 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2545,30 +2542,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C2" t="s">
         <v>42</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2576,16 +2573,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C3" t="s">
         <v>42</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -2593,16 +2590,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C4" t="s">
         <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2610,16 +2607,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2627,16 +2624,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C6" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -2644,16 +2641,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>42</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -2661,16 +2658,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -2678,16 +2675,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -2695,16 +2692,16 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -2712,16 +2709,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -2729,16 +2726,16 @@
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -2746,10 +2743,10 @@
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>42</v>
@@ -2773,267 +2770,267 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B80AA7-E63F-4277-90B1-5BE1C0EFE54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FA857C-EACC-49E5-98D9-46F52701595B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="171">
   <si>
     <t>James Craven</t>
   </si>
@@ -535,13 +535,37 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Alex Herrera</t>
+  </si>
+  <si>
+    <t>Alex Shuleschenko</t>
+  </si>
+  <si>
+    <t>Alex St. Pierre</t>
+  </si>
+  <si>
+    <t>Alex Krakovsky</t>
+  </si>
+  <si>
+    <t>Alex Lerer</t>
+  </si>
+  <si>
+    <t>Alex Orlean</t>
+  </si>
+  <si>
+    <t>Alex Raskin</t>
+  </si>
+  <si>
+    <t>Alex Sullivan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,6 +596,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -651,7 +682,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -672,6 +703,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,14 +986,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -972,7 +1004,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -988,13 +1020,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1002,12 +1034,12 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>157</v>
       </c>
@@ -1020,13 +1052,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FB3C8-D05A-4A1D-9559-104A9F0AD28A}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="56.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="56.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>158</v>
       </c>
@@ -1034,7 +1066,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>160</v>
       </c>
@@ -1042,7 +1074,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>160</v>
       </c>
@@ -1058,13 +1090,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1075,7 +1107,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -1086,7 +1118,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1102,17 +1134,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1125,22 +1157,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1154,28 +1186,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.28515625" customWidth="1"/>
+    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1267,7 +1299,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1362,7 +1394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1457,7 +1489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1552,7 +1584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1647,7 +1679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1742,7 +1774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1837,7 +1869,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1932,7 +1964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -2027,7 +2059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2122,7 +2154,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -2217,7 +2249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
@@ -2312,7 +2344,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
@@ -2417,37 +2449,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>71</v>
       </c>
@@ -2460,19 +2492,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -2498,7 +2530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -2532,15 +2564,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
@@ -2554,7 +2586,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>98</v>
       </c>
@@ -2571,7 +2603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>98</v>
       </c>
@@ -2588,7 +2620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>98</v>
       </c>
@@ -2605,7 +2637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>98</v>
       </c>
@@ -2622,7 +2654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>98</v>
       </c>
@@ -2639,7 +2671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>98</v>
       </c>
@@ -2656,7 +2688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>98</v>
       </c>
@@ -2673,7 +2705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>98</v>
       </c>
@@ -2690,7 +2722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>98</v>
       </c>
@@ -2707,7 +2739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>98</v>
       </c>
@@ -2724,7 +2756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>98</v>
       </c>
@@ -2741,7 +2773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>98</v>
       </c>
@@ -2762,273 +2794,302 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF4DCB0-85D6-4076-87FF-4126675E54C9}">
-  <dimension ref="A1:A53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>169</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" s="12" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>154</v>
       </c>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FA857C-EACC-49E5-98D9-46F52701595B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680D6EA8-847E-40C9-A0D8-AF1861CFB1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -986,14 +986,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>108</v>
       </c>
@@ -1020,13 +1020,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1034,12 +1034,12 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>157</v>
       </c>
@@ -1052,13 +1052,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FB3C8-D05A-4A1D-9559-104A9F0AD28A}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="1" max="1" width="56.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>158</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>160</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>160</v>
       </c>
@@ -1090,13 +1090,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1134,17 +1134,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1157,22 +1157,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1186,28 +1186,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.33203125" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
@@ -2449,37 +2449,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>71</v>
       </c>
@@ -2492,19 +2492,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -2564,15 +2564,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>98</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>98</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>98</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>98</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>98</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>98</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>98</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>98</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>98</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>98</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>98</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>98</v>
       </c>
@@ -2795,49 +2795,49 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF4DCB0-85D6-4076-87FF-4126675E54C9}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>163</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>111</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>166</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -2877,62 +2877,62 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>167</v>
       </c>
@@ -2940,67 +2940,67 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>168</v>
       </c>
@@ -3008,32 +3008,32 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>169</v>
       </c>
@@ -3041,47 +3041,47 @@
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>170</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>154</v>
       </c>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680D6EA8-847E-40C9-A0D8-AF1861CFB1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE93584-8284-44DB-BEC3-63B192489DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="172">
   <si>
     <t>James Craven</t>
   </si>
@@ -559,6 +559,9 @@
   </si>
   <si>
     <t>Alex Sullivan</t>
+  </si>
+  <si>
+    <t>Chris1 Lord1</t>
   </si>
 </sst>
 </file>
@@ -2532,7 +2535,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE93584-8284-44DB-BEC3-63B192489DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738D4813-E2CA-4546-A84A-34E45D5F0976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -87,9 +87,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -534,9 +531,6 @@
     <t>52</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Alex Herrera</t>
   </si>
   <si>
@@ -562,6 +556,12 @@
   </si>
   <si>
     <t>Chris1 Lord1</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
   </si>
 </sst>
 </file>
@@ -989,14 +989,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1004,12 +1004,12 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1023,28 +1023,28 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1055,34 +1055,34 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FB3C8-D05A-4A1D-9559-104A9F0AD28A}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="56.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="56.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B2" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1093,13 +1093,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1107,26 +1107,26 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1137,17 +1137,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1160,24 +1160,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1189,28 +1189,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.28515625" customWidth="1"/>
+    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1221,1222 +1221,1222 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
         <v>75</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC1" s="1" t="s">
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>107</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC2" t="s">
         <v>80</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" t="s">
-        <v>108</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W2" t="s">
-        <v>49</v>
-      </c>
-      <c r="X2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AD2" t="s">
         <v>51</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>52</v>
       </c>
       <c r="AE2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" t="s">
         <v>38</v>
       </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
       <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s">
         <v>40</v>
       </c>
-      <c r="G3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L3" t="s">
         <v>41</v>
       </c>
-      <c r="I3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" t="s">
+        <v>107</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y3" t="s">
         <v>76</v>
       </c>
-      <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" t="s">
-        <v>108</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U3" t="s">
-        <v>47</v>
-      </c>
-      <c r="V3" t="s">
-        <v>48</v>
-      </c>
-      <c r="W3" t="s">
-        <v>49</v>
-      </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>50</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="AB3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" t="s">
         <v>38</v>
       </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>162</v>
-      </c>
-      <c r="E4" t="s">
-        <v>39</v>
-      </c>
       <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" t="s">
         <v>40</v>
       </c>
-      <c r="G4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" t="s">
         <v>41</v>
       </c>
-      <c r="I4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" t="s">
+        <v>107</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y4" t="s">
         <v>76</v>
       </c>
-      <c r="L4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" t="s">
-        <v>108</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U4" t="s">
-        <v>47</v>
-      </c>
-      <c r="V4" t="s">
-        <v>48</v>
-      </c>
-      <c r="W4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X4" t="s">
+      <c r="Z4" t="s">
         <v>50</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AA4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AB4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD4" t="s">
         <v>51</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>52</v>
       </c>
       <c r="AE4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>162</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
-      </c>
       <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L5" t="s">
         <v>41</v>
       </c>
-      <c r="I5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" t="s">
+        <v>107</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U5" t="s">
+        <v>46</v>
+      </c>
+      <c r="V5" t="s">
+        <v>47</v>
+      </c>
+      <c r="W5" t="s">
+        <v>48</v>
+      </c>
+      <c r="X5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y5" t="s">
         <v>76</v>
       </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" t="s">
-        <v>108</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R5" t="s">
-        <v>45</v>
-      </c>
-      <c r="S5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U5" t="s">
-        <v>47</v>
-      </c>
-      <c r="V5" t="s">
-        <v>48</v>
-      </c>
-      <c r="W5" t="s">
-        <v>49</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="Z5" t="s">
         <v>50</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="AA5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z5" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA5" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="AB5" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E6" t="s">
-        <v>39</v>
-      </c>
       <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
         <v>40</v>
       </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" t="s">
+        <v>75</v>
+      </c>
+      <c r="L6" t="s">
         <v>41</v>
       </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S6" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U6" t="s">
+        <v>46</v>
+      </c>
+      <c r="V6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W6" t="s">
+        <v>48</v>
+      </c>
+      <c r="X6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y6" t="s">
         <v>76</v>
       </c>
-      <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" t="s">
-        <v>108</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" t="s">
-        <v>45</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U6" t="s">
-        <v>47</v>
-      </c>
-      <c r="V6" t="s">
-        <v>48</v>
-      </c>
-      <c r="W6" t="s">
-        <v>49</v>
-      </c>
-      <c r="X6" t="s">
+      <c r="Z6" t="s">
         <v>50</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AA6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AB6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD6" t="s">
         <v>51</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>52</v>
       </c>
       <c r="AE6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
       <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L7" t="s">
         <v>41</v>
       </c>
-      <c r="I7" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S7" t="s">
+        <v>44</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" t="s">
+        <v>46</v>
+      </c>
+      <c r="V7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W7" t="s">
+        <v>48</v>
+      </c>
+      <c r="X7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y7" t="s">
         <v>76</v>
       </c>
-      <c r="L7" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7" t="s">
-        <v>108</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R7" t="s">
-        <v>45</v>
-      </c>
-      <c r="S7" t="s">
-        <v>45</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U7" t="s">
-        <v>47</v>
-      </c>
-      <c r="V7" t="s">
-        <v>48</v>
-      </c>
-      <c r="W7" t="s">
-        <v>49</v>
-      </c>
-      <c r="X7" t="s">
+      <c r="Z7" t="s">
         <v>50</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="AA7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="AB7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" t="s">
         <v>38</v>
       </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>162</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
       <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="s">
         <v>40</v>
       </c>
-      <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>75</v>
+      </c>
+      <c r="L8" t="s">
         <v>41</v>
       </c>
-      <c r="I8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" t="s">
+        <v>107</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R8" t="s">
+        <v>44</v>
+      </c>
+      <c r="S8" t="s">
+        <v>44</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U8" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W8" t="s">
+        <v>48</v>
+      </c>
+      <c r="X8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y8" t="s">
         <v>76</v>
       </c>
-      <c r="L8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8" t="s">
-        <v>108</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R8" t="s">
-        <v>45</v>
-      </c>
-      <c r="S8" t="s">
-        <v>45</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" t="s">
-        <v>47</v>
-      </c>
-      <c r="V8" t="s">
-        <v>48</v>
-      </c>
-      <c r="W8" t="s">
-        <v>49</v>
-      </c>
-      <c r="X8" t="s">
+      <c r="Z8" t="s">
         <v>50</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AA8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AB8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD8" t="s">
         <v>51</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>52</v>
       </c>
       <c r="AE8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
       <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
         <v>40</v>
       </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" t="s">
         <v>41</v>
       </c>
-      <c r="I9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" t="s">
+        <v>107</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R9" t="s">
+        <v>44</v>
+      </c>
+      <c r="S9" t="s">
+        <v>44</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U9" t="s">
+        <v>46</v>
+      </c>
+      <c r="V9" t="s">
+        <v>47</v>
+      </c>
+      <c r="W9" t="s">
+        <v>48</v>
+      </c>
+      <c r="X9" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y9" t="s">
         <v>76</v>
       </c>
-      <c r="L9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" t="s">
-        <v>108</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R9" t="s">
-        <v>45</v>
-      </c>
-      <c r="S9" t="s">
-        <v>45</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U9" t="s">
-        <v>47</v>
-      </c>
-      <c r="V9" t="s">
-        <v>48</v>
-      </c>
-      <c r="W9" t="s">
-        <v>49</v>
-      </c>
-      <c r="X9" t="s">
+      <c r="Z9" t="s">
         <v>50</v>
       </c>
-      <c r="Y9" t="s">
+      <c r="AA9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="AB9" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AD9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E10" t="s">
-        <v>39</v>
-      </c>
       <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
         <v>40</v>
       </c>
-      <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" t="s">
+        <v>75</v>
+      </c>
+      <c r="L10" t="s">
         <v>41</v>
       </c>
-      <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N10" t="s">
+        <v>107</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R10" t="s">
+        <v>44</v>
+      </c>
+      <c r="S10" t="s">
+        <v>44</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U10" t="s">
+        <v>46</v>
+      </c>
+      <c r="V10" t="s">
+        <v>47</v>
+      </c>
+      <c r="W10" t="s">
+        <v>48</v>
+      </c>
+      <c r="X10" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y10" t="s">
         <v>76</v>
       </c>
-      <c r="L10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M10" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10" t="s">
-        <v>108</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R10" t="s">
-        <v>45</v>
-      </c>
-      <c r="S10" t="s">
-        <v>45</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U10" t="s">
-        <v>47</v>
-      </c>
-      <c r="V10" t="s">
-        <v>48</v>
-      </c>
-      <c r="W10" t="s">
-        <v>49</v>
-      </c>
-      <c r="X10" t="s">
+      <c r="Z10" t="s">
         <v>50</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="AA10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="AB10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD10" t="s">
         <v>51</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>52</v>
       </c>
       <c r="AE10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>162</v>
-      </c>
-      <c r="E11" t="s">
-        <v>39</v>
-      </c>
       <c r="F11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" t="s">
         <v>40</v>
       </c>
-      <c r="G11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" t="s">
+        <v>75</v>
+      </c>
+      <c r="L11" t="s">
         <v>41</v>
       </c>
-      <c r="I11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" t="s">
+        <v>107</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R11" t="s">
+        <v>44</v>
+      </c>
+      <c r="S11" t="s">
+        <v>44</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U11" t="s">
+        <v>46</v>
+      </c>
+      <c r="V11" t="s">
+        <v>47</v>
+      </c>
+      <c r="W11" t="s">
+        <v>48</v>
+      </c>
+      <c r="X11" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y11" t="s">
         <v>76</v>
       </c>
-      <c r="L11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" t="s">
-        <v>43</v>
-      </c>
-      <c r="N11" t="s">
-        <v>108</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R11" t="s">
-        <v>45</v>
-      </c>
-      <c r="S11" t="s">
-        <v>45</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U11" t="s">
-        <v>47</v>
-      </c>
-      <c r="V11" t="s">
-        <v>48</v>
-      </c>
-      <c r="W11" t="s">
-        <v>49</v>
-      </c>
-      <c r="X11" t="s">
+      <c r="Z11" t="s">
         <v>50</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="AA11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AB11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD11" t="s">
         <v>51</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>52</v>
       </c>
       <c r="AE11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="F12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K12" s="4" t="s">
+      <c r="M12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" t="s">
+        <v>107</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U12" t="s">
+        <v>46</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N12" t="s">
-        <v>108</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U12" t="s">
-        <v>47</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X12" s="4" t="s">
+      <c r="Z12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y12" s="4" t="s">
+      <c r="AA12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z12" s="4" t="s">
+      <c r="AB12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD12" t="s">
         <v>51</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>52</v>
       </c>
       <c r="AE12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
-        <v>162</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="F13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K13" s="4" t="s">
+      <c r="M13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13" t="s">
+        <v>107</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U13" t="s">
+        <v>46</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y13" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N13" t="s">
-        <v>108</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U13" t="s">
-        <v>47</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="X13" s="4" t="s">
+      <c r="Z13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y13" s="4" t="s">
+      <c r="AA13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z13" s="4" t="s">
+      <c r="AB13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD13" t="s">
         <v>51</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>52</v>
       </c>
       <c r="AE13">
         <v>12</v>
@@ -2452,39 +2452,39 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2495,68 +2495,68 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>60</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2567,224 +2567,224 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="B2" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -2798,303 +2798,303 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF4DCB0-85D6-4076-87FF-4126675E54C9}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B11" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B24" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B37" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>167</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>168</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>169</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B52" s="12" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>170</v>
-      </c>
-      <c r="B52" s="12" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738D4813-E2CA-4546-A84A-34E45D5F0976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7BDC43-AA60-414C-9256-091766D806F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="171">
   <si>
     <t>James Craven</t>
   </si>
@@ -553,9 +553,6 @@
   </si>
   <si>
     <t>Alex Sullivan</t>
-  </si>
-  <si>
-    <t>Chris1 Lord1</t>
   </si>
   <si>
     <t>CSDN-0000007327</t>
@@ -1221,7 +1218,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1313,7 +1310,7 @@
         <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -1408,7 +1405,7 @@
         <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -1503,7 +1500,7 @@
         <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
@@ -1598,7 +1595,7 @@
         <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
@@ -1693,7 +1690,7 @@
         <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -1788,7 +1785,7 @@
         <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -1883,7 +1880,7 @@
         <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -1978,7 +1975,7 @@
         <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -2073,7 +2070,7 @@
         <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -2168,7 +2165,7 @@
         <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -2263,7 +2260,7 @@
         <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>38</v>
@@ -2358,7 +2355,7 @@
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>38</v>
@@ -2535,7 +2532,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7BDC43-AA60-414C-9256-091766D806F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BD10EF-505C-4DC6-95F1-6FB14B3A1573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -555,10 +555,10 @@
     <t>Alex Sullivan</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
-  </si>
-  <si>
     <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -986,14 +986,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>107</v>
       </c>
@@ -1020,13 +1020,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -1034,12 +1034,12 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>156</v>
       </c>
@@ -1052,13 +1052,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FB3C8-D05A-4A1D-9559-104A9F0AD28A}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="1" max="1" width="56.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>157</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>159</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>159</v>
       </c>
@@ -1090,13 +1090,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>72</v>
       </c>
@@ -1134,17 +1134,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1157,22 +1157,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1186,28 +1186,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.33203125" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1299,7 +1299,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -1394,7 +1394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -1489,7 +1489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
@@ -1584,7 +1584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
@@ -1679,7 +1679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -1774,7 +1774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -1964,7 +1964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -2059,7 +2059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -2154,7 +2154,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -2249,7 +2249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>38</v>
@@ -2344,7 +2344,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>37</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>38</v>
@@ -2449,37 +2449,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>70</v>
       </c>
@@ -2492,19 +2492,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2564,15 +2564,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>93</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>97</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>97</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>97</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>97</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>97</v>
       </c>
@@ -2671,7 +2671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>97</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>97</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>97</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>97</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>97</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>97</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>97</v>
       </c>
@@ -2795,49 +2795,49 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF4DCB0-85D6-4076-87FF-4126675E54C9}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>161</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>109</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>110</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>164</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>112</v>
       </c>
@@ -2877,62 +2877,62 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>165</v>
       </c>
@@ -2940,67 +2940,67 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>166</v>
       </c>
@@ -3008,32 +3008,32 @@
         <v>137</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -3041,47 +3041,47 @@
         <v>143</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>168</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>153</v>
       </c>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BD10EF-505C-4DC6-95F1-6FB14B3A1573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC82243C-B2AA-4E02-84A4-51CFFB168D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="167">
   <si>
     <t>James Craven</t>
   </si>
@@ -318,12 +318,6 @@
     <t>FA - Portfolio-Auto Struct Prd/Consulting</t>
   </si>
   <si>
-    <t>CVAS - IP Valuation</t>
-  </si>
-  <si>
-    <t>TAS - ESG Due Diligence &amp; Analytics</t>
-  </si>
-  <si>
     <t>System Admin</t>
   </si>
   <si>
@@ -343,12 +337,6 @@
   </si>
   <si>
     <t>Portfolio Valuation</t>
-  </si>
-  <si>
-    <t>CVAS - Corporate Valuation Advisory Services</t>
-  </si>
-  <si>
-    <t>TAS - Due Diligence Services</t>
   </si>
   <si>
     <t>OppDealTeamMembers</t>
@@ -986,14 +974,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1004,9 +992,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1020,28 +1008,28 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1052,34 +1040,34 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FB3C8-D05A-4A1D-9559-104A9F0AD28A}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="56.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="56.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1090,13 +1078,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1107,7 +1095,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -1118,12 +1106,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1134,17 +1122,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1157,22 +1145,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1185,29 +1173,29 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
-  <dimension ref="A1:AE13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.28515625" customWidth="1"/>
+    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1218,7 +1206,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1299,7 +1287,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1310,7 +1298,7 @@
         <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -1340,7 +1328,7 @@
         <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>43</v>
@@ -1394,7 +1382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -1405,7 +1393,7 @@
         <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -1435,7 +1423,7 @@
         <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>43</v>
@@ -1489,7 +1477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1500,7 +1488,7 @@
         <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
@@ -1530,7 +1518,7 @@
         <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>43</v>
@@ -1584,7 +1572,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -1595,7 +1583,7 @@
         <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
@@ -1625,7 +1613,7 @@
         <v>42</v>
       </c>
       <c r="N5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>43</v>
@@ -1679,7 +1667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -1690,7 +1678,7 @@
         <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -1720,7 +1708,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>43</v>
@@ -1774,7 +1762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1785,7 +1773,7 @@
         <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -1815,7 +1803,7 @@
         <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>43</v>
@@ -1869,7 +1857,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -1880,7 +1868,7 @@
         <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -1910,7 +1898,7 @@
         <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>43</v>
@@ -1964,7 +1952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1975,7 +1963,7 @@
         <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -2005,7 +1993,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>43</v>
@@ -2059,7 +2047,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -2070,7 +2058,7 @@
         <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -2100,7 +2088,7 @@
         <v>42</v>
       </c>
       <c r="N10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>43</v>
@@ -2154,7 +2142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -2165,7 +2153,7 @@
         <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -2195,7 +2183,7 @@
         <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>43</v>
@@ -2247,196 +2235,6 @@
       </c>
       <c r="AE11">
         <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N12" t="s">
-        <v>107</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U12" t="s">
-        <v>46</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="W12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="X12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y12" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N13" t="s">
-        <v>107</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U13" t="s">
-        <v>46</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE13">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2449,37 +2247,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>70</v>
       </c>
@@ -2492,19 +2290,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -2530,7 +2328,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2563,35 +2361,35 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="9" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>41</v>
@@ -2603,12 +2401,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
         <v>41</v>
@@ -2620,12 +2418,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
@@ -2637,12 +2435,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
         <v>41</v>
@@ -2654,12 +2452,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
@@ -2671,12 +2469,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
@@ -2688,12 +2486,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
@@ -2705,12 +2503,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
@@ -2722,12 +2520,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
@@ -2739,12 +2537,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
         <v>41</v>
@@ -2754,37 +2552,6 @@
       </c>
       <c r="E11">
         <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2795,303 +2562,303 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF4DCB0-85D6-4076-87FF-4126675E54C9}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B24" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B37" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B43" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B52" s="12" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>165</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>166</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>167</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>168</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA40EE2-98D9-4E61-8C72-EB4142DF2B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D72455C-5700-4801-A556-1F6AD0607050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="OppDealTeamMembers" sheetId="21" r:id="rId9"/>
     <sheet name="Roles" sheetId="22" r:id="rId10"/>
     <sheet name="OverlimitMessage" sheetId="23" r:id="rId11"/>
+    <sheet name="Notes" sheetId="24" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="173">
   <si>
     <t>James Craven</t>
   </si>
@@ -547,6 +548,24 @@
   </si>
   <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Lorriane Johnson</t>
+  </si>
+  <si>
+    <t>Compliance User</t>
+  </si>
+  <si>
+    <t>Christine Sha</t>
+  </si>
+  <si>
+    <t>Legal User</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Legal Hold test Notes</t>
   </si>
 </sst>
 </file>
@@ -1075,13 +1094,36 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBD923E-8299-4450-B2D0-D9E2AE16D359}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1112,6 +1154,22 @@
       </c>
       <c r="B3" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D72455C-5700-4801-A556-1F6AD0607050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638087AE-E166-4023-B63C-10184959F379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -283,9 +283,6 @@
     <t>10000</t>
   </si>
   <si>
-    <t>Liz Hedgcock</t>
-  </si>
-  <si>
     <t>Tombstone Permission</t>
   </si>
   <si>
@@ -566,6 +563,9 @@
   </si>
   <si>
     <t>Legal Hold test Notes</t>
+  </si>
+  <si>
+    <t>Blaise Brunda</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1038,17 +1038,17 @@
         <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1067,26 +1067,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1104,12 +1104,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1153,23 +1153,23 @@
         <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" t="s">
         <v>167</v>
-      </c>
-      <c r="B4" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" t="s">
         <v>169</v>
-      </c>
-      <c r="B5" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1264,7 +1264,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1339,7 +1339,7 @@
         <v>35</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>36</v>
@@ -1356,7 +1356,7 @@
         <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -1386,7 +1386,7 @@
         <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>43</v>
@@ -1431,7 +1431,7 @@
         <v>77</v>
       </c>
       <c r="AC2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD2" t="s">
         <v>51</v>
@@ -1448,10 +1448,10 @@
         <v>37</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -1481,7 +1481,7 @@
         <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>43</v>
@@ -1526,7 +1526,7 @@
         <v>77</v>
       </c>
       <c r="AC3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD3" t="s">
         <v>39</v>
@@ -1543,10 +1543,10 @@
         <v>37</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>43</v>
@@ -1621,7 +1621,7 @@
         <v>77</v>
       </c>
       <c r="AC4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD4" t="s">
         <v>51</v>
@@ -1638,10 +1638,10 @@
         <v>37</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
@@ -1671,7 +1671,7 @@
         <v>42</v>
       </c>
       <c r="N5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>43</v>
@@ -1716,7 +1716,7 @@
         <v>77</v>
       </c>
       <c r="AC5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD5" t="s">
         <v>39</v>
@@ -1733,10 +1733,10 @@
         <v>37</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -1766,7 +1766,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>43</v>
@@ -1811,7 +1811,7 @@
         <v>77</v>
       </c>
       <c r="AC6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD6" t="s">
         <v>51</v>
@@ -1828,10 +1828,10 @@
         <v>37</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -1861,7 +1861,7 @@
         <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>43</v>
@@ -1906,7 +1906,7 @@
         <v>77</v>
       </c>
       <c r="AC7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD7" t="s">
         <v>39</v>
@@ -1923,10 +1923,10 @@
         <v>37</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -1956,7 +1956,7 @@
         <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>43</v>
@@ -2001,7 +2001,7 @@
         <v>77</v>
       </c>
       <c r="AC8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD8" t="s">
         <v>51</v>
@@ -2018,10 +2018,10 @@
         <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -2051,7 +2051,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>43</v>
@@ -2096,7 +2096,7 @@
         <v>77</v>
       </c>
       <c r="AC9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD9" t="s">
         <v>39</v>
@@ -2113,10 +2113,10 @@
         <v>37</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -2146,7 +2146,7 @@
         <v>42</v>
       </c>
       <c r="N10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>43</v>
@@ -2191,7 +2191,7 @@
         <v>77</v>
       </c>
       <c r="AC10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD10" t="s">
         <v>51</v>
@@ -2208,10 +2208,10 @@
         <v>37</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -2241,7 +2241,7 @@
         <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>43</v>
@@ -2286,7 +2286,7 @@
         <v>77</v>
       </c>
       <c r="AC11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AD11" t="s">
         <v>51</v>
@@ -2430,24 +2430,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C2" t="s">
         <v>41</v>
@@ -2461,16 +2461,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C3" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -2478,16 +2478,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2495,16 +2495,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C5" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2512,16 +2512,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -2529,16 +2529,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -2546,16 +2546,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -2563,16 +2563,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -2580,16 +2580,16 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -2597,16 +2597,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="C11" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -2629,294 +2629,294 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638087AE-E166-4023-B63C-10184959F379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754AEB46-C973-49AE-9335-A12E3428CBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -265,9 +265,6 @@
     <t>Engagements</t>
   </si>
   <si>
-    <t>Indrajeet Singh</t>
-  </si>
-  <si>
     <t>FA - Portfolio-Advis/Consulting</t>
   </si>
   <si>
@@ -566,6 +563,9 @@
   </si>
   <si>
     <t>Blaise Brunda</t>
+  </si>
+  <si>
+    <t>Ajay Nair</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1038,17 +1038,17 @@
         <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1067,26 +1067,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -1104,12 +1104,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1150,26 +1150,26 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" t="s">
         <v>166</v>
-      </c>
-      <c r="B4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s">
         <v>168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1264,7 +1264,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1330,7 +1330,7 @@
         <v>33</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>34</v>
@@ -1339,7 +1339,7 @@
         <v>35</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>36</v>
@@ -1353,10 +1353,10 @@
         <v>37</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -1377,7 +1377,7 @@
         <v>39</v>
       </c>
       <c r="K2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L2" t="s">
         <v>41</v>
@@ -1386,7 +1386,7 @@
         <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>43</v>
@@ -1419,19 +1419,19 @@
         <v>49</v>
       </c>
       <c r="Y2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z2" t="s">
         <v>50</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD2" t="s">
         <v>51</v>
@@ -1448,10 +1448,10 @@
         <v>37</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -1472,7 +1472,7 @@
         <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L3" t="s">
         <v>41</v>
@@ -1481,7 +1481,7 @@
         <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>43</v>
@@ -1514,19 +1514,19 @@
         <v>49</v>
       </c>
       <c r="Y3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z3" t="s">
         <v>50</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD3" t="s">
         <v>39</v>
@@ -1543,10 +1543,10 @@
         <v>37</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
@@ -1567,7 +1567,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s">
         <v>41</v>
@@ -1576,7 +1576,7 @@
         <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>43</v>
@@ -1609,19 +1609,19 @@
         <v>49</v>
       </c>
       <c r="Y4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z4" t="s">
         <v>50</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD4" t="s">
         <v>51</v>
@@ -1638,10 +1638,10 @@
         <v>37</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
@@ -1662,7 +1662,7 @@
         <v>39</v>
       </c>
       <c r="K5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L5" t="s">
         <v>41</v>
@@ -1671,7 +1671,7 @@
         <v>42</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>43</v>
@@ -1704,19 +1704,19 @@
         <v>49</v>
       </c>
       <c r="Y5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z5" t="s">
         <v>50</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD5" t="s">
         <v>39</v>
@@ -1733,10 +1733,10 @@
         <v>37</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -1757,7 +1757,7 @@
         <v>39</v>
       </c>
       <c r="K6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L6" t="s">
         <v>41</v>
@@ -1766,7 +1766,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>43</v>
@@ -1799,19 +1799,19 @@
         <v>49</v>
       </c>
       <c r="Y6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z6" t="s">
         <v>50</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD6" t="s">
         <v>51</v>
@@ -1828,10 +1828,10 @@
         <v>37</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -1852,7 +1852,7 @@
         <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L7" t="s">
         <v>41</v>
@@ -1861,7 +1861,7 @@
         <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>43</v>
@@ -1894,19 +1894,19 @@
         <v>49</v>
       </c>
       <c r="Y7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z7" t="s">
         <v>50</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD7" t="s">
         <v>39</v>
@@ -1923,10 +1923,10 @@
         <v>37</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -1947,7 +1947,7 @@
         <v>39</v>
       </c>
       <c r="K8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L8" t="s">
         <v>41</v>
@@ -1956,7 +1956,7 @@
         <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>43</v>
@@ -1989,19 +1989,19 @@
         <v>49</v>
       </c>
       <c r="Y8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z8" t="s">
         <v>50</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD8" t="s">
         <v>51</v>
@@ -2018,10 +2018,10 @@
         <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -2042,7 +2042,7 @@
         <v>39</v>
       </c>
       <c r="K9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>41</v>
@@ -2051,7 +2051,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>43</v>
@@ -2084,19 +2084,19 @@
         <v>49</v>
       </c>
       <c r="Y9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z9" t="s">
         <v>50</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD9" t="s">
         <v>39</v>
@@ -2113,10 +2113,10 @@
         <v>37</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -2137,7 +2137,7 @@
         <v>39</v>
       </c>
       <c r="K10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L10" t="s">
         <v>41</v>
@@ -2146,7 +2146,7 @@
         <v>42</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>43</v>
@@ -2179,19 +2179,19 @@
         <v>49</v>
       </c>
       <c r="Y10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z10" t="s">
         <v>50</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD10" t="s">
         <v>51</v>
@@ -2208,10 +2208,10 @@
         <v>37</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -2232,7 +2232,7 @@
         <v>39</v>
       </c>
       <c r="K11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L11" t="s">
         <v>41</v>
@@ -2241,7 +2241,7 @@
         <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>43</v>
@@ -2274,19 +2274,19 @@
         <v>49</v>
       </c>
       <c r="Y11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z11" t="s">
         <v>50</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD11" t="s">
         <v>51</v>
@@ -2430,30 +2430,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C2" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -2461,16 +2461,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C3" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -2478,16 +2478,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -2495,16 +2495,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C5" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2512,16 +2512,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -2529,16 +2529,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -2546,16 +2546,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -2563,16 +2563,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -2580,16 +2580,16 @@
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -2597,16 +2597,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="C11" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -2629,294 +2629,294 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754AEB46-C973-49AE-9335-A12E3428CBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9DB5B8-91A6-4102-A8B6-603FEBE6729D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -1231,7 +1231,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -1250,10 +1250,9 @@
     <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1345,7 +1344,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1436,11 +1435,8 @@
       <c r="AD2" t="s">
         <v>51</v>
       </c>
-      <c r="AE2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -1531,11 +1527,8 @@
       <c r="AD3" t="s">
         <v>39</v>
       </c>
-      <c r="AE3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1626,11 +1619,8 @@
       <c r="AD4" t="s">
         <v>51</v>
       </c>
-      <c r="AE4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -1721,11 +1711,8 @@
       <c r="AD5" t="s">
         <v>39</v>
       </c>
-      <c r="AE5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -1816,11 +1803,8 @@
       <c r="AD6" t="s">
         <v>51</v>
       </c>
-      <c r="AE6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1911,11 +1895,8 @@
       <c r="AD7" t="s">
         <v>39</v>
       </c>
-      <c r="AE7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -2006,11 +1987,8 @@
       <c r="AD8" t="s">
         <v>51</v>
       </c>
-      <c r="AE8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -2101,11 +2079,8 @@
       <c r="AD9" t="s">
         <v>39</v>
       </c>
-      <c r="AE9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -2196,11 +2171,8 @@
       <c r="AD10" t="s">
         <v>51</v>
       </c>
-      <c r="AE10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -2290,9 +2262,6 @@
       </c>
       <c r="AD11" t="s">
         <v>51</v>
-      </c>
-      <c r="AE11">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A9DB5B8-91A6-4102-A8B6-603FEBE6729D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC5326D-6DEB-4CB0-8D2E-D2C5EBB31E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -1124,6 +1124,7 @@
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC5326D-6DEB-4CB0-8D2E-D2C5EBB31E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B3C58B-C4BC-40C8-A352-65FF2D9EA8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="450" windowWidth="29070" windowHeight="15570" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B3C58B-C4BC-40C8-A352-65FF2D9EA8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E7E937-B96D-495F-AB35-BD418B510C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="450" windowWidth="29070" windowHeight="15570" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="173">
   <si>
     <t>James Craven</t>
   </si>
@@ -298,21 +298,6 @@
     <t>FA - Portfolio-Diligence/Assets</t>
   </si>
   <si>
-    <t>FA - Portfolio-Funds Transfer</t>
-  </si>
-  <si>
-    <t>FA - Portfolio-GP interest</t>
-  </si>
-  <si>
-    <t>FA - Portfolio-Real Estate</t>
-  </si>
-  <si>
-    <t>FA - Portfolio-Valuation</t>
-  </si>
-  <si>
-    <t>FA - Portfolio-Auto Struct Prd/Consulting</t>
-  </si>
-  <si>
     <t>System Admin</t>
   </si>
   <si>
@@ -325,9 +310,6 @@
     <t>HLEntity</t>
   </si>
   <si>
-    <t>UpdateJobType</t>
-  </si>
-  <si>
     <t>Retained</t>
   </si>
   <si>
@@ -566,6 +548,24 @@
   </si>
   <si>
     <t>Ajay Nair</t>
+  </si>
+  <si>
+    <t>TAS - ESG Due Diligence &amp; Analytics</t>
+  </si>
+  <si>
+    <t>TAS - Lender Services</t>
+  </si>
+  <si>
+    <t>TAS - Tax</t>
+  </si>
+  <si>
+    <t>TAS - Due Diligence-Buyside Add-On</t>
+  </si>
+  <si>
+    <t>TAS - Due Diligence-Sellside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAS - Due Diligence Services </t>
   </si>
 </sst>
 </file>
@@ -689,7 +689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -711,6 +711,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1013,7 +1014,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1038,17 +1039,17 @@
         <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -1067,26 +1068,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1104,12 +1105,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -1140,7 +1141,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1151,26 +1152,26 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1253,7 +1254,7 @@
     <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1264,7 +1265,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1352,11 +1353,11 @@
       <c r="B2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -1386,7 +1387,7 @@
         <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>43</v>
@@ -1444,11 +1445,11 @@
       <c r="B3" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" t="s">
         <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -1478,7 +1479,7 @@
         <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>43</v>
@@ -1536,11 +1537,11 @@
       <c r="B4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" t="s">
         <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
@@ -1570,7 +1571,7 @@
         <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>43</v>
@@ -1628,11 +1629,11 @@
       <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" t="s">
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
@@ -1662,7 +1663,7 @@
         <v>42</v>
       </c>
       <c r="N5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>43</v>
@@ -1720,11 +1721,11 @@
       <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" t="s">
         <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -1754,7 +1755,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>43</v>
@@ -1812,11 +1813,11 @@
       <c r="B7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>83</v>
+      <c r="C7" t="s">
+        <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -1846,7 +1847,7 @@
         <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>43</v>
@@ -1904,11 +1905,11 @@
       <c r="B8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>84</v>
+      <c r="C8" t="s">
+        <v>168</v>
       </c>
       <c r="D8" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -1938,7 +1939,7 @@
         <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>43</v>
@@ -1996,11 +1997,11 @@
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>85</v>
+      <c r="C9" t="s">
+        <v>169</v>
       </c>
       <c r="D9" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -2030,7 +2031,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>43</v>
@@ -2081,18 +2082,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
       <c r="B10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>86</v>
+      <c r="C10" t="s">
+        <v>170</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -2122,7 +2123,7 @@
         <v>42</v>
       </c>
       <c r="N10" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>43</v>
@@ -2180,11 +2181,11 @@
       <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>87</v>
+      <c r="C11" t="s">
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -2214,7 +2215,7 @@
         <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>43</v>
@@ -2400,184 +2401,162 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>92</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>72</v>
-      </c>
+      <c r="D2" s="5"/>
       <c r="E2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>79</v>
-      </c>
+      <c r="D3" s="6"/>
       <c r="E3">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>80</v>
-      </c>
+      <c r="D4" s="6"/>
       <c r="E4">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>81</v>
-      </c>
+      <c r="D5" s="6"/>
       <c r="E5">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>82</v>
-      </c>
+      <c r="D6" s="6"/>
       <c r="E6">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>83</v>
-      </c>
+      <c r="D7" s="6"/>
       <c r="E7">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>84</v>
-      </c>
+      <c r="D8" s="6"/>
       <c r="E8">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>85</v>
-      </c>
+      <c r="D9" s="6"/>
       <c r="E9">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>86</v>
-      </c>
+      <c r="D10" s="7"/>
       <c r="E10">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>172</v>
       </c>
       <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>87</v>
-      </c>
+      <c r="D11" s="8"/>
       <c r="E11">
         <v>10</v>
       </c>
@@ -2599,294 +2578,294 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E7E937-B96D-495F-AB35-BD418B510C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CB60E3-A7B0-445A-8F2A-03F011E3B600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="Roles" sheetId="22" r:id="rId10"/>
     <sheet name="OverlimitMessage" sheetId="23" r:id="rId11"/>
     <sheet name="Notes" sheetId="24" r:id="rId12"/>
+    <sheet name="OppTASPrjStage" sheetId="25" r:id="rId13"/>
+    <sheet name="EngTASPrjStage" sheetId="26" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="186">
   <si>
     <t>James Craven</t>
   </si>
@@ -566,6 +568,45 @@
   </si>
   <si>
     <t xml:space="preserve">TAS - Due Diligence Services </t>
+  </si>
+  <si>
+    <t>Opportunity TAS Project Stage</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Active Opportunity</t>
+  </si>
+  <si>
+    <t>Closed Opportunity – Deal Died</t>
+  </si>
+  <si>
+    <t>Closed Opportunity – Lost to Competitor</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
+    <t>Dead – Deal Died After Engagement</t>
+  </si>
+  <si>
+    <t>Engaged – Ongoing</t>
+  </si>
+  <si>
+    <t>Engaged – On hold – Awaiting Data</t>
+  </si>
+  <si>
+    <t>Engaged – On hold – Deal Issues</t>
+  </si>
+  <si>
+    <t>Engaged – On hold – Market Issue</t>
+  </si>
+  <si>
+    <t>Work completed – Client did not Move Forward</t>
+  </si>
+  <si>
+    <t>Work completed – Transaction Occurred</t>
   </si>
 </sst>
 </file>
@@ -1118,6 +1159,102 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4441AC86-366C-40F8-9BCC-E2B3B63AF008}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071B5EE3-B9AA-4965-8B0B-FE910633BA18}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C5"/>

--- a/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
+++ b/TestData/LV_T1432_OpportunityToEngagementConversionMappingForFVAJobTypes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CB60E3-A7B0-445A-8F2A-03F011E3B600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1468DD0C-131E-4F81-A09C-18F58585BBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -21,12 +21,9 @@
     <sheet name="InternalTeams" sheetId="18" r:id="rId6"/>
     <sheet name="AddContact" sheetId="14" r:id="rId7"/>
     <sheet name="Engagement" sheetId="20" r:id="rId8"/>
-    <sheet name="OppDealTeamMembers" sheetId="21" r:id="rId9"/>
-    <sheet name="Roles" sheetId="22" r:id="rId10"/>
-    <sheet name="OverlimitMessage" sheetId="23" r:id="rId11"/>
-    <sheet name="Notes" sheetId="24" r:id="rId12"/>
-    <sheet name="OppTASPrjStage" sheetId="25" r:id="rId13"/>
-    <sheet name="EngTASPrjStage" sheetId="26" r:id="rId14"/>
+    <sheet name="Notes" sheetId="24" r:id="rId9"/>
+    <sheet name="OppTASPrjStage" sheetId="25" r:id="rId10"/>
+    <sheet name="EngTASPrjStage" sheetId="26" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="119">
   <si>
     <t>James Craven</t>
   </si>
@@ -318,210 +315,9 @@
     <t>Portfolio Valuation</t>
   </si>
   <si>
-    <t>OppDealTeamMembers</t>
-  </si>
-  <si>
-    <t>Elaine Pan</t>
-  </si>
-  <si>
-    <t>Aaron Schultz</t>
-  </si>
-  <si>
-    <t>Ben Chiu</t>
-  </si>
-  <si>
-    <t>Blair Richardson</t>
-  </si>
-  <si>
-    <t>Conrad Kolasa</t>
-  </si>
-  <si>
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>Jason Vierig</t>
-  </si>
-  <si>
-    <t>Karim Jooma</t>
-  </si>
-  <si>
-    <t>Kyle Poorman</t>
-  </si>
-  <si>
-    <t>Marshall Taylor</t>
-  </si>
-  <si>
-    <t>Matt Kavney</t>
-  </si>
-  <si>
-    <t>Matt Sturgell</t>
-  </si>
-  <si>
-    <t>Michael Chiu</t>
-  </si>
-  <si>
-    <t>Ozzie Ozdemir</t>
-  </si>
-  <si>
-    <t>Paul Birchwood</t>
-  </si>
-  <si>
-    <t>Prashant Kamath</t>
-  </si>
-  <si>
-    <t>Preston Wolf</t>
-  </si>
-  <si>
-    <t>Ali Amin</t>
-  </si>
-  <si>
-    <t>Rittik Chakrabarti</t>
-  </si>
-  <si>
-    <t>Robert Zarnoch</t>
-  </si>
-  <si>
-    <t>Ryan Verola</t>
-  </si>
-  <si>
-    <t>Ryan Mahlan</t>
-  </si>
-  <si>
-    <t>Sid Chitnis</t>
-  </si>
-  <si>
-    <t>Susanna O'Brien</t>
-  </si>
-  <si>
-    <t>Zach Hamilton</t>
-  </si>
-  <si>
-    <t>Rebecca Hu</t>
-  </si>
-  <si>
-    <t>Timothy Kang</t>
-  </si>
-  <si>
-    <t>Abhinav Pal</t>
-  </si>
-  <si>
-    <t>Adam Dunayer</t>
-  </si>
-  <si>
-    <t>Adam Ishola</t>
-  </si>
-  <si>
-    <t>Adam Schor</t>
-  </si>
-  <si>
-    <t>Aditi Singh</t>
-  </si>
-  <si>
-    <t>Aditya Aiyer</t>
-  </si>
-  <si>
-    <t>Aditya Tyagi</t>
-  </si>
-  <si>
-    <t>Adnan Sura</t>
-  </si>
-  <si>
-    <t>Adriana Stacey</t>
-  </si>
-  <si>
-    <t>Afnan Ahmed</t>
-  </si>
-  <si>
-    <t>Ahmed Elbiltagui</t>
-  </si>
-  <si>
-    <t>Aidan Fitzgibbon</t>
-  </si>
-  <si>
-    <t>AJ Amankwaa</t>
-  </si>
-  <si>
-    <t>Ajay Arelli</t>
-  </si>
-  <si>
-    <t>Akshat Jamad</t>
-  </si>
-  <si>
-    <t>Alex Dochter</t>
-  </si>
-  <si>
-    <t>Alberico Altieri</t>
-  </si>
-  <si>
-    <t>Allen Plunk</t>
-  </si>
-  <si>
-    <t>Albert Sung</t>
-  </si>
-  <si>
-    <t>Alfonso Garcia</t>
-  </si>
-  <si>
-    <t>Aleksandra Chadam</t>
-  </si>
-  <si>
-    <t>Alessandro Ciravegna</t>
-  </si>
-  <si>
-    <t>Alessandro Rossi</t>
-  </si>
-  <si>
-    <t>Alexander Garcia</t>
-  </si>
-  <si>
-    <t>Alex Cohen</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Analyst</t>
-  </si>
-  <si>
-    <t>Associate</t>
-  </si>
-  <si>
-    <t>OverlimitMessage</t>
-  </si>
-  <si>
-    <t>MaxMembersLimit</t>
-  </si>
-  <si>
-    <t>Please remove and re-add the following deal team member(s) to the internal team and then add the desired role(s). Removing the deal team member will allow the Office Allocation field to re-populate.</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>Alex Herrera</t>
-  </si>
-  <si>
-    <t>Alex Shuleschenko</t>
-  </si>
-  <si>
-    <t>Alex St. Pierre</t>
-  </si>
-  <si>
-    <t>Alex Krakovsky</t>
-  </si>
-  <si>
-    <t>Alex Lerer</t>
-  </si>
-  <si>
-    <t>Alex Orlean</t>
-  </si>
-  <si>
-    <t>Alex Raskin</t>
-  </si>
-  <si>
-    <t>Alex Sullivan</t>
-  </si>
-  <si>
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
@@ -567,9 +363,6 @@
     <t>TAS - Due Diligence-Sellside</t>
   </si>
   <si>
-    <t xml:space="preserve">TAS - Due Diligence Services </t>
-  </si>
-  <si>
     <t>Opportunity TAS Project Stage</t>
   </si>
   <si>
@@ -607,13 +400,16 @@
   </si>
   <si>
     <t>Work completed – Transaction Occurred</t>
+  </si>
+  <si>
+    <t>TAS - Due Diligence Services</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -644,13 +440,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -730,7 +519,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -745,13 +534,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1055,7 +837,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1067,99 +849,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{938FB3C8-D05A-4A1D-9559-104A9F0AD28A}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="56.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBD923E-8299-4450-B2D0-D9E2AE16D359}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4441AC86-366C-40F8-9BCC-E2B3B63AF008}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1169,27 +858,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1197,7 +886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071B5EE3-B9AA-4965-8B0B-FE910633BA18}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1207,47 +896,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1278,7 +967,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -1289,7 +978,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
         <v>83</v>
@@ -1297,18 +986,18 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1402,7 +1091,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -1494,7 +1183,7 @@
         <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -1524,7 +1213,7 @@
         <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>43</v>
@@ -1586,7 +1275,7 @@
         <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -1616,7 +1305,7 @@
         <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>43</v>
@@ -1678,7 +1367,7 @@
         <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>38</v>
@@ -1708,7 +1397,7 @@
         <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>43</v>
@@ -1770,7 +1459,7 @@
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>38</v>
@@ -1800,7 +1489,7 @@
         <v>42</v>
       </c>
       <c r="N5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>43</v>
@@ -1862,7 +1551,7 @@
         <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>38</v>
@@ -1892,7 +1581,7 @@
         <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>43</v>
@@ -1951,10 +1640,10 @@
         <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
@@ -1984,7 +1673,7 @@
         <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>43</v>
@@ -2043,10 +1732,10 @@
         <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -2076,7 +1765,7 @@
         <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>43</v>
@@ -2135,10 +1824,10 @@
         <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -2168,7 +1857,7 @@
         <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>43</v>
@@ -2227,10 +1916,10 @@
         <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -2260,7 +1949,7 @@
         <v>42</v>
       </c>
       <c r="N10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>43</v>
@@ -2319,10 +2008,10 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -2352,7 +2041,7 @@
         <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>43</v>
@@ -2597,7 +2286,7 @@
       <c r="A5" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C5" t="s">
@@ -2612,7 +2301,7 @@
       <c r="A6" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C6" t="s">
@@ -2627,8 +2316,8 @@
       <c r="A7" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>172</v>
+      <c r="B7" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
@@ -2642,8 +2331,8 @@
       <c r="A8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>172</v>
+      <c r="B8" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
@@ -2657,8 +2346,8 @@
       <c r="A9" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>172</v>
+      <c r="B9" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
@@ -2672,8 +2361,8 @@
       <c r="A10" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>172</v>
+      <c r="B10" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="C10" t="s">
         <v>41</v>
@@ -2687,8 +2376,8 @@
       <c r="A11" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>172</v>
+      <c r="B11" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="C11" t="s">
         <v>41</v>
@@ -2704,305 +2393,21 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AF4DCB0-85D6-4076-87FF-4126675E54C9}">
-  <dimension ref="A1:D53"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBD923E-8299-4450-B2D0-D9E2AE16D359}">
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
         <v>97</v>
-      </c>
-      <c r="D9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>153</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>154</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>155</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>156</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>
